--- a/output/pdf_financials_xlsx/OLV.xlsx
+++ b/output/pdf_financials_xlsx/OLV.xlsx
@@ -1086,28 +1086,28 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.026293</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.038477</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.016716</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.017497</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.017292</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.027516</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.025826</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.008898</v>
       </c>
     </row>
     <row r="13">
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.875426</v>
+        <v>-0.901719</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.217607</v>
+        <v>-1.256084</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.470813</v>
+        <v>-0.487529</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.32798</v>
+        <v>-0.345477</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.372942</v>
+        <v>-0.390234</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.708986</v>
+        <v>-0.736502</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.653474</v>
+        <v>0.627648</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.488316</v>
+        <v>-0.497214</v>
       </c>
     </row>
     <row r="28">
@@ -2186,28 +2186,28 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.875426</v>
+        <v>-0.901719</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.217607</v>
+        <v>-1.256084</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.470813</v>
+        <v>-0.487529</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.32798</v>
+        <v>-0.345477</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.372942</v>
+        <v>-0.390234</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.708986</v>
+        <v>-0.736502</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.653474</v>
+        <v>0.627648</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.488316</v>
+        <v>-0.497214</v>
       </c>
     </row>
     <row r="30">
@@ -2486,10 +2486,10 @@
         <v>0.755663</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.5518459999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.250802</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.08</v>
@@ -2513,10 +2513,10 @@
         <v>0.478203</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.690418</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.239386</v>
       </c>
     </row>
     <row r="35">
@@ -2602,10 +2602,10 @@
         <v>0.755663</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.5518459999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.250802</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.08</v>
@@ -2629,10 +2629,10 @@
         <v>0.478203</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.690418</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.239386</v>
       </c>
     </row>
     <row r="37">
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.36656</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.034085</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.7024010000000001</v>
+        <v>0.011983</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.256113</v>
+        <v>0.016727</v>
       </c>
     </row>
     <row r="49">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -31022,7 +31022,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -31867,7 +31867,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
